--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFEC150-A635-43D0-B34B-AF61F17E8864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD378D0-B93B-4169-BCD5-FC30E81540B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32985" yWindow="2475" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33705" yWindow="1725" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="270">
   <si>
     <t>SKU</t>
   </si>
@@ -523,12 +523,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£678.81</t>
   </si>
   <si>
@@ -827,6 +821,15 @@
   </si>
   <si>
     <t>£58.25</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
+  </si>
+  <si>
+    <t>£276.59</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1273,7 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
         <v>90</v>
@@ -1279,7 +1282,7 @@
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J2" t="s">
         <v>135</v>
@@ -1291,22 +1294,22 @@
         <v>89</v>
       </c>
       <c r="M2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="O2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P2" t="s">
         <v>81</v>
       </c>
       <c r="Q2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="R2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1326,7 +1329,7 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G3" t="s">
         <v>91</v>
@@ -1335,7 +1338,7 @@
         <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J3" t="s">
         <v>136</v>
@@ -1347,22 +1350,22 @@
         <v>89</v>
       </c>
       <c r="M3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P3" t="s">
         <v>81</v>
       </c>
       <c r="Q3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1382,7 +1385,7 @@
         <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G4" t="s">
         <v>92</v>
@@ -1403,22 +1406,22 @@
         <v>89</v>
       </c>
       <c r="M4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="O4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P4" t="s">
         <v>81</v>
       </c>
       <c r="Q4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="R4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1438,7 +1441,7 @@
         <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G5" t="s">
         <v>93</v>
@@ -1459,22 +1462,22 @@
         <v>89</v>
       </c>
       <c r="M5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P5" t="s">
         <v>81</v>
       </c>
       <c r="Q5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1494,7 +1497,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G6" t="s">
         <v>94</v>
@@ -1515,22 +1518,22 @@
         <v>89</v>
       </c>
       <c r="M6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P6" t="s">
         <v>81</v>
       </c>
       <c r="Q6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="R6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1550,7 +1553,7 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G7" t="s">
         <v>95</v>
@@ -1559,7 +1562,7 @@
         <v>113</v>
       </c>
       <c r="I7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J7" t="s">
         <v>140</v>
@@ -1571,22 +1574,22 @@
         <v>89</v>
       </c>
       <c r="M7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N7" t="s">
         <v>81</v>
       </c>
       <c r="O7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P7" t="s">
         <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1606,7 +1609,7 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G8" t="s">
         <v>95</v>
@@ -1627,13 +1630,13 @@
         <v>89</v>
       </c>
       <c r="M8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="O8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P8" t="s">
         <v>81</v>
@@ -1642,7 +1645,7 @@
         <v>81</v>
       </c>
       <c r="R8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1662,7 +1665,7 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G9" t="s">
         <v>96</v>
@@ -1671,7 +1674,7 @@
         <v>114</v>
       </c>
       <c r="I9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J9" t="s">
         <v>142</v>
@@ -1683,22 +1686,22 @@
         <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P9" t="s">
         <v>81</v>
       </c>
       <c r="Q9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1718,7 +1721,7 @@
         <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G10" t="s">
         <v>97</v>
@@ -1745,16 +1748,16 @@
         <v>81</v>
       </c>
       <c r="O10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P10" t="s">
         <v>81</v>
       </c>
       <c r="Q10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1774,7 +1777,7 @@
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G11" t="s">
         <v>98</v>
@@ -1795,22 +1798,22 @@
         <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P11" t="s">
         <v>81</v>
       </c>
       <c r="Q11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1830,7 +1833,7 @@
         <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G12" t="s">
         <v>99</v>
@@ -1851,7 +1854,7 @@
         <v>89</v>
       </c>
       <c r="M12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N12" t="s">
         <v>81</v>
@@ -1863,7 +1866,7 @@
         <v>81</v>
       </c>
       <c r="Q12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="R12" t="s">
         <v>89</v>
@@ -1886,7 +1889,7 @@
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G13" t="s">
         <v>100</v>
@@ -1907,22 +1910,22 @@
         <v>89</v>
       </c>
       <c r="M13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P13" t="s">
         <v>81</v>
       </c>
       <c r="Q13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1942,7 +1945,7 @@
         <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G14" t="s">
         <v>101</v>
@@ -1963,19 +1966,19 @@
         <v>89</v>
       </c>
       <c r="M14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P14" t="s">
         <v>81</v>
       </c>
       <c r="Q14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="R14" t="s">
         <v>89</v>
@@ -1998,7 +2001,7 @@
         <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G15" t="s">
         <v>102</v>
@@ -2019,19 +2022,19 @@
         <v>89</v>
       </c>
       <c r="M15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="O15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P15" t="s">
         <v>81</v>
       </c>
       <c r="Q15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R15" t="s">
         <v>89</v>
@@ -2054,7 +2057,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G16" t="s">
         <v>103</v>
@@ -2075,22 +2078,22 @@
         <v>89</v>
       </c>
       <c r="M16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s">
         <v>81</v>
       </c>
       <c r="Q16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2101,7 +2104,7 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="D17" t="s">
         <v>81</v>
@@ -2190,10 +2193,10 @@
         <v>89</v>
       </c>
       <c r="N18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s">
         <v>81</v>
@@ -2202,7 +2205,7 @@
         <v>89</v>
       </c>
       <c r="R18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2246,10 +2249,10 @@
         <v>89</v>
       </c>
       <c r="N19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s">
         <v>81</v>
@@ -2258,7 +2261,7 @@
         <v>89</v>
       </c>
       <c r="R19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2461,19 +2464,19 @@
         <v>89</v>
       </c>
       <c r="K23" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s">
         <v>89</v>
       </c>
       <c r="M23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P23" t="s">
         <v>89</v>
@@ -2482,7 +2485,7 @@
         <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2517,7 +2520,7 @@
         <v>89</v>
       </c>
       <c r="K24" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="L24" t="s">
         <v>89</v>
@@ -2526,10 +2529,10 @@
         <v>81</v>
       </c>
       <c r="N24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P24" t="s">
         <v>89</v>
@@ -2538,7 +2541,7 @@
         <v>89</v>
       </c>
       <c r="R24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2573,7 +2576,7 @@
         <v>89</v>
       </c>
       <c r="K25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s">
         <v>89</v>
@@ -2582,10 +2585,10 @@
         <v>81</v>
       </c>
       <c r="N25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P25" t="s">
         <v>89</v>
@@ -2594,7 +2597,7 @@
         <v>89</v>
       </c>
       <c r="R25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
